--- a/public/static/型号导入模板.xlsx
+++ b/public/static/型号导入模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="型号导入模板" sheetId="1" r:id="rId1"/>
@@ -33,6 +33,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>型号(</t>
     </r>
     <r>
@@ -58,7 +65,7 @@
   </si>
   <si>
     <r>
-      <t>内圈规格型号(</t>
+      <t>内圈品名规格(</t>
     </r>
     <r>
       <rPr>
@@ -83,7 +90,7 @@
   </si>
   <si>
     <r>
-      <t>外圈规格型号(</t>
+      <t>外圈品名规格(</t>
     </r>
     <r>
       <rPr>
@@ -108,7 +115,7 @@
   </si>
   <si>
     <r>
-      <t>钢球规格型号(</t>
+      <t>钢球品名规格(</t>
     </r>
     <r>
       <rPr>
@@ -133,6 +140,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>钢球用量(</t>
     </r>
     <r>
@@ -158,6 +172,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>油脂用量（</t>
     </r>
     <r>
@@ -183,6 +204,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>保持架用量（</t>
     </r>
     <r>
@@ -1451,15 +1479,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="7.33333333333333" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20.5555555555556" customWidth="1"/>
-    <col min="3" max="3" width="25.8888888888889" customWidth="1"/>
-    <col min="4" max="4" width="27.5555555555556" customWidth="1"/>
-    <col min="5" max="5" width="23.2222222222222" customWidth="1"/>
-    <col min="6" max="6" width="19.4444444444444" customWidth="1"/>
-    <col min="7" max="7" width="20.7777777777778" customWidth="1"/>
+    <col min="2" max="2" width="20.5583333333333" customWidth="1"/>
+    <col min="3" max="3" width="25.8916666666667" customWidth="1"/>
+    <col min="4" max="4" width="27.5583333333333" customWidth="1"/>
+    <col min="5" max="5" width="23.225" customWidth="1"/>
+    <col min="6" max="6" width="19.4416666666667" customWidth="1"/>
+    <col min="7" max="7" width="20.775" customWidth="1"/>
     <col min="8" max="8" width="23" customWidth="1"/>
   </cols>
   <sheetData>

--- a/public/static/型号导入模板.xlsx
+++ b/public/static/型号导入模板.xlsx
@@ -65,6 +65,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>内圈品名规格(</t>
     </r>
     <r>
@@ -90,6 +97,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>外圈品名规格(</t>
     </r>
     <r>
@@ -115,6 +129,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>钢球品名规格(</t>
     </r>
     <r>
@@ -172,14 +193,7 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>油脂用量（</t>
+      <t>油脂用量(</t>
     </r>
     <r>
       <rPr>
@@ -195,23 +209,16 @@
       <rPr>
         <b/>
         <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>）</t>
+        <color theme="0"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>)</t>
     </r>
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>保持架用量（</t>
+      <t>保持架用量(</t>
     </r>
     <r>
       <rPr>
@@ -227,11 +234,11 @@
       <rPr>
         <b/>
         <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>）</t>
+        <color theme="0"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>)</t>
     </r>
   </si>
   <si>
@@ -248,7 +255,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -437,6 +444,13 @@
       <b/>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
